--- a/VerveStacks_NGA_grids_kan10/SuppXLS/Scen_TSParameters_ts_12t.xlsx
+++ b/VerveStacks_NGA_grids_kan10/SuppXLS/Scen_TSParameters_ts_12t.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{584F599F-B3AF-4C11-8519-8F5FE9917E0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{22A363B6-B9AE-44C3-9E95-50C384A8CC59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -711,10 +711,10 @@
     <t>day_night</t>
   </si>
   <si>
-    <t>SaD,FaD,WaP,WaD,RaD,FaP,SaP,RaP</t>
-  </si>
-  <si>
-    <t>FaP,SaP,RaP,RaN,WaP,FaN,SaN,WaN</t>
+    <t>FaP,SaP,RaD,SaD,RaP,FaD,WaD,WaP</t>
+  </si>
+  <si>
+    <t>FaP,SaP,SaN,WaN,WaP,RaP,FaN,RaN</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>FaP,SaP,RaP,RaN,WaP,FaN,SaN,WaN</v>
+        <v>FaP,SaP,SaN,WaN,WaP,RaP,FaN,RaN</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>SaD,FaD,WaP,WaD,RaD,FaP,SaP,RaP</v>
+        <v>FaP,SaP,RaD,SaD,RaP,FaD,WaD,WaP</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1437,7 +1437,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7760B779-1F20-4971-BC35-75C797CE9E21}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D2D1767-7C39-4DBE-8670-0A20BA43D405}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1521,7 +1521,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F940A75-739C-4821-8698-5C80B7A6E2C0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC6DAA92-4BDF-48D5-8E4E-C71649F996DB}">
   <dimension ref="B9:O442"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -12959,7 +12959,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{654EE4A4-0A97-4D52-9050-04F9BAB9090E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D57F34E-E249-4422-A28B-DAD1A94477D8}">
   <dimension ref="B9:BL83"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -20357,7 +20357,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A464BBE-B7B1-4A1B-895A-1F4146B31BA7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B609B349-71A7-49DC-B90E-E74C4E6A3ABC}">
   <dimension ref="B9:E22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -20555,7 +20555,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFD5511D-6877-42D2-B7DD-9308604CDFEE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E4231A9-F889-4536-B274-62A57DCEACAA}">
   <dimension ref="B9:D34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -20846,7 +20846,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{043B25BD-285A-48AF-A701-3E59DCFD8EF4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{860913BF-A79E-49B8-A37B-986A316CB420}">
   <dimension ref="B9:D22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -21005,7 +21005,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8DF0259-9E79-4C8E-9531-6CD22261B29C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A132E14E-C2E9-4768-BC63-106499C59F24}">
   <dimension ref="B9:E126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -21387,7 +21387,7 @@
         <v>41</v>
       </c>
       <c r="D36">
-        <v>0.27806666666666668</v>
+        <v>0.27806666666666663</v>
       </c>
       <c r="E36" t="s">
         <v>230</v>
@@ -21443,7 +21443,7 @@
         <v>41</v>
       </c>
       <c r="D40">
-        <v>0.28116666666666668</v>
+        <v>0.28116666666666662</v>
       </c>
       <c r="E40" t="s">
         <v>230</v>
@@ -21555,7 +21555,7 @@
         <v>41</v>
       </c>
       <c r="D48">
-        <v>0.33253333333333335</v>
+        <v>0.33253333333333329</v>
       </c>
       <c r="E48" t="s">
         <v>230</v>
@@ -21667,7 +21667,7 @@
         <v>41</v>
       </c>
       <c r="D56">
-        <v>0.27503333333333335</v>
+        <v>0.2750333333333333</v>
       </c>
       <c r="E56" t="s">
         <v>230</v>
@@ -22115,7 +22115,7 @@
         <v>41</v>
       </c>
       <c r="D88">
-        <v>0.23103333333333331</v>
+        <v>0.23103333333333334</v>
       </c>
       <c r="E88" t="s">
         <v>230</v>
@@ -22171,7 +22171,7 @@
         <v>41</v>
       </c>
       <c r="D92">
-        <v>0.28523333333333334</v>
+        <v>0.28523333333333328</v>
       </c>
       <c r="E92" t="s">
         <v>230</v>
@@ -22283,7 +22283,7 @@
         <v>41</v>
       </c>
       <c r="D100">
-        <v>0.40036666666666659</v>
+        <v>0.4003666666666667</v>
       </c>
       <c r="E100" t="s">
         <v>230</v>
@@ -22563,7 +22563,7 @@
         <v>41</v>
       </c>
       <c r="D120">
-        <v>0.29799999999999999</v>
+        <v>0.29800000000000004</v>
       </c>
       <c r="E120" t="s">
         <v>230</v>
